--- a/data/SCRAPING_REKAP_DAMPAK_BENCANA_ENDE_LATEST.xlsx
+++ b/data/SCRAPING_REKAP_DAMPAK_BENCANA_ENDE_LATEST.xlsx
@@ -17041,7 +17041,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -17126,7 +17126,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -17209,7 +17209,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -17292,7 +17292,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -17375,7 +17375,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -17545,7 +17545,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -17628,7 +17628,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -17711,7 +17711,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -17794,7 +17794,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -17877,7 +17877,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -17960,7 +17960,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -18043,7 +18043,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -18126,7 +18126,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -18209,7 +18209,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -18292,7 +18292,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -18375,7 +18375,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -18458,7 +18458,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -18541,7 +18541,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -18624,7 +18624,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -18707,7 +18707,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -18790,7 +18790,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -18873,7 +18873,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -18956,7 +18956,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -19039,7 +19039,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -19122,7 +19122,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -19205,7 +19205,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -19288,7 +19288,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -19371,7 +19371,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -19454,7 +19454,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -19539,7 +19539,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -19622,7 +19622,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -19705,7 +19705,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -19788,7 +19788,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -19871,7 +19871,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -19954,7 +19954,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -20037,7 +20037,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -20120,7 +20120,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -20203,7 +20203,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -20286,7 +20286,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -20369,7 +20369,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -20452,7 +20452,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -20535,7 +20535,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -20618,7 +20618,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -20701,7 +20701,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -20784,7 +20784,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -20867,7 +20867,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -20950,7 +20950,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -21033,7 +21033,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -21116,7 +21116,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -21199,7 +21199,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -21282,7 +21282,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -21365,7 +21365,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -21448,7 +21448,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -21531,7 +21531,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -21614,7 +21614,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -21697,7 +21697,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -21780,7 +21780,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -21865,7 +21865,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -21948,7 +21948,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -22031,7 +22031,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -22114,7 +22114,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -22197,7 +22197,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -22280,7 +22280,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -22363,7 +22363,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -22446,7 +22446,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -22529,7 +22529,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -22612,7 +22612,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -22695,7 +22695,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -22778,7 +22778,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -22861,7 +22861,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -22944,7 +22944,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -23027,7 +23027,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -23110,7 +23110,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -23193,7 +23193,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -23276,7 +23276,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -23361,7 +23361,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -23446,7 +23446,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -23529,7 +23529,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -23614,7 +23614,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -23701,7 +23701,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -23784,7 +23784,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -23867,7 +23867,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -23950,7 +23950,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -24037,7 +24037,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -24120,7 +24120,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -24203,7 +24203,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24286,7 +24286,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -24369,7 +24369,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -24452,7 +24452,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -24535,7 +24535,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -24618,7 +24618,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -24701,7 +24701,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -24784,7 +24784,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -24867,7 +24867,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -24950,7 +24950,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -25037,7 +25037,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -25120,7 +25120,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -25203,7 +25203,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -25286,7 +25286,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -25369,7 +25369,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -25452,7 +25452,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -25535,7 +25535,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -25618,7 +25618,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -25701,7 +25701,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -25784,7 +25784,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -25867,7 +25867,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -25950,7 +25950,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -26033,7 +26033,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -26118,7 +26118,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -26201,7 +26201,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -26284,7 +26284,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -26367,7 +26367,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -26450,7 +26450,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -26533,7 +26533,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -26616,7 +26616,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -26699,7 +26699,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -26782,7 +26782,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -26865,7 +26865,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -26950,7 +26950,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -27033,7 +27033,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -27116,7 +27116,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -27199,7 +27199,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -27282,7 +27282,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -27365,7 +27365,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -27448,7 +27448,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -27535,7 +27535,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -27618,7 +27618,7 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -27701,7 +27701,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -27786,7 +27786,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -27869,7 +27869,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -27952,7 +27952,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -28035,7 +28035,7 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -28118,7 +28118,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -28201,7 +28201,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -28284,7 +28284,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -28367,7 +28367,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -28450,7 +28450,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -28533,7 +28533,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -28616,7 +28616,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -28699,7 +28699,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -28782,7 +28782,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -28865,7 +28865,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -28948,7 +28948,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -29033,7 +29033,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -29116,7 +29116,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -29199,7 +29199,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -29282,7 +29282,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -29365,7 +29365,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -29448,7 +29448,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -29533,7 +29533,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -29616,7 +29616,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -29699,7 +29699,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -29782,7 +29782,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -29865,7 +29865,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -29948,7 +29948,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -30031,7 +30031,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -30114,7 +30114,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -30197,7 +30197,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -30280,7 +30280,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -30365,7 +30365,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -30448,7 +30448,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -30531,7 +30531,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -30614,7 +30614,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -30697,7 +30697,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -30784,7 +30784,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -30867,7 +30867,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -30950,7 +30950,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -31033,7 +31033,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -31118,7 +31118,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -31201,7 +31201,7 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -31284,7 +31284,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -31367,7 +31367,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -31450,7 +31450,7 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -31533,7 +31533,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -31616,7 +31616,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -31699,7 +31699,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -31782,7 +31782,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -31865,7 +31865,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -31948,7 +31948,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -32031,7 +32031,7 @@
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -32116,7 +32116,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -32199,7 +32199,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -32282,7 +32282,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -32365,7 +32365,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -32448,7 +32448,7 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -32531,7 +32531,7 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -32614,7 +32614,7 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -32697,7 +32697,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -32780,7 +32780,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -32863,7 +32863,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -32946,7 +32946,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -33029,7 +33029,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -33112,7 +33112,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -33195,7 +33195,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -33278,7 +33278,7 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -33361,7 +33361,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -33446,7 +33446,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -33531,7 +33531,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -33614,7 +33614,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -33697,7 +33697,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -33780,7 +33780,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -33863,7 +33863,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:31</t>
+          <t>2026-10-22 12:11:02</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -34059,7 +34059,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -34112,7 +34112,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -34165,7 +34165,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -34218,7 +34218,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -34271,7 +34271,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -34324,7 +34324,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -34377,7 +34377,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -34430,7 +34430,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -34483,7 +34483,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -34536,7 +34536,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -34589,7 +34589,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -34642,7 +34642,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -34695,7 +34695,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -34748,7 +34748,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -34801,7 +34801,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -34854,7 +34854,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -34907,7 +34907,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -34960,7 +34960,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -35013,7 +35013,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -35066,7 +35066,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -35119,7 +35119,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -35172,7 +35172,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -35225,7 +35225,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -35278,7 +35278,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -35331,7 +35331,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -35384,7 +35384,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -35437,7 +35437,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -35490,7 +35490,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -35543,7 +35543,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -35596,7 +35596,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -35649,7 +35649,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -35755,7 +35755,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -35808,7 +35808,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -35861,7 +35861,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -35914,7 +35914,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -35967,7 +35967,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -36020,7 +36020,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -36073,7 +36073,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -36126,7 +36126,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -36179,7 +36179,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -36232,7 +36232,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -36285,7 +36285,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -36338,7 +36338,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -36391,7 +36391,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -36444,7 +36444,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -36497,7 +36497,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -36550,7 +36550,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -36603,7 +36603,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -36656,7 +36656,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -36709,7 +36709,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -36762,7 +36762,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -36815,7 +36815,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -36868,7 +36868,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -36921,7 +36921,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -36974,7 +36974,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -37027,7 +37027,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -37080,7 +37080,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -37133,7 +37133,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -37186,7 +37186,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -37239,7 +37239,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -37292,7 +37292,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -37345,7 +37345,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -37398,7 +37398,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -37451,7 +37451,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -37504,7 +37504,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -37557,7 +37557,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -37610,7 +37610,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -37663,7 +37663,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -37716,7 +37716,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -37769,7 +37769,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -37822,7 +37822,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -37875,7 +37875,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -37928,7 +37928,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -37981,7 +37981,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -38034,7 +38034,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -38087,7 +38087,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -38140,7 +38140,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -38193,7 +38193,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -38246,7 +38246,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -38299,7 +38299,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -38352,7 +38352,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -38405,7 +38405,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -38458,7 +38458,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -38511,7 +38511,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -38564,7 +38564,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -38617,7 +38617,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -38670,7 +38670,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -38723,7 +38723,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -38776,7 +38776,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -38829,7 +38829,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -38882,7 +38882,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -38935,7 +38935,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -38988,7 +38988,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -39041,7 +39041,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -39094,7 +39094,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -39147,7 +39147,7 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -39200,7 +39200,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -39253,7 +39253,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -39306,7 +39306,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -39359,7 +39359,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -39412,7 +39412,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -39465,7 +39465,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -39518,7 +39518,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -39571,7 +39571,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -39624,7 +39624,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -39677,7 +39677,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -39730,7 +39730,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -39783,7 +39783,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -39836,7 +39836,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -39889,7 +39889,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -39942,7 +39942,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -39995,7 +39995,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -40048,7 +40048,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -40101,7 +40101,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -40154,7 +40154,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -40207,7 +40207,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -40260,7 +40260,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -40313,7 +40313,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -40366,7 +40366,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -40419,7 +40419,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -40472,7 +40472,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -40525,7 +40525,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -40578,7 +40578,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -40631,7 +40631,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -40684,7 +40684,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -40737,7 +40737,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -40790,7 +40790,7 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -40843,7 +40843,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -40896,7 +40896,7 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -40949,7 +40949,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -41002,7 +41002,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -41055,7 +41055,7 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -41108,7 +41108,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -41161,7 +41161,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -41214,7 +41214,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -41320,7 +41320,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -41373,7 +41373,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -41426,7 +41426,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -41479,7 +41479,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -41532,7 +41532,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -41585,7 +41585,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -41638,7 +41638,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -41691,7 +41691,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -41744,7 +41744,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -41797,7 +41797,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -41850,7 +41850,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -41903,7 +41903,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -41956,7 +41956,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -42009,7 +42009,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -42062,7 +42062,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -42115,7 +42115,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -42168,7 +42168,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -42221,7 +42221,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -42274,7 +42274,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -42327,7 +42327,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -42380,7 +42380,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -42433,7 +42433,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -42486,7 +42486,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -42539,7 +42539,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -42592,7 +42592,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -42645,7 +42645,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -42698,7 +42698,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -42751,7 +42751,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -42804,7 +42804,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -42857,7 +42857,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -42910,7 +42910,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -42963,7 +42963,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -43016,7 +43016,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -43069,7 +43069,7 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -43122,7 +43122,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -43175,7 +43175,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -43228,7 +43228,7 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -43281,7 +43281,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -43334,7 +43334,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -43387,7 +43387,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -43440,7 +43440,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -43493,7 +43493,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -43546,7 +43546,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -43599,7 +43599,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -43652,7 +43652,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -43705,7 +43705,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -43758,7 +43758,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -43811,7 +43811,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -43864,7 +43864,7 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -43917,7 +43917,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -43970,7 +43970,7 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -44023,7 +44023,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -44076,7 +44076,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -44129,7 +44129,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -44182,7 +44182,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -44235,7 +44235,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -44288,7 +44288,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -44341,7 +44341,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -44394,7 +44394,7 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -44447,7 +44447,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -44500,7 +44500,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -44553,7 +44553,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -44606,7 +44606,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -44659,7 +44659,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -44712,7 +44712,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -44765,7 +44765,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -44818,7 +44818,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -44871,7 +44871,7 @@
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -44924,7 +44924,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -44977,7 +44977,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -45030,7 +45030,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -45083,7 +45083,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -45136,7 +45136,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -45189,7 +45189,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -45242,7 +45242,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -45295,7 +45295,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -45348,7 +45348,7 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -45401,7 +45401,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -45454,7 +45454,7 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -45507,7 +45507,7 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -45560,7 +45560,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -45613,7 +45613,7 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -45666,7 +45666,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -45719,7 +45719,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -45772,7 +45772,7 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -45825,7 +45825,7 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -45878,7 +45878,7 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -45931,7 +45931,7 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -45984,7 +45984,7 @@
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -46037,7 +46037,7 @@
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -46090,7 +46090,7 @@
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -46143,7 +46143,7 @@
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -46196,7 +46196,7 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -46249,7 +46249,7 @@
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -46302,7 +46302,7 @@
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -46355,7 +46355,7 @@
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -46408,7 +46408,7 @@
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -46461,7 +46461,7 @@
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -46514,7 +46514,7 @@
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -46567,7 +46567,7 @@
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -46620,7 +46620,7 @@
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -46673,7 +46673,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -46726,7 +46726,7 @@
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -46779,7 +46779,7 @@
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -46832,7 +46832,7 @@
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -46885,7 +46885,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -46938,7 +46938,7 @@
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -46991,7 +46991,7 @@
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -47044,7 +47044,7 @@
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -47097,7 +47097,7 @@
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -47150,7 +47150,7 @@
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -47203,7 +47203,7 @@
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -47256,7 +47256,7 @@
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -47309,7 +47309,7 @@
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -47362,7 +47362,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -47415,7 +47415,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -47468,7 +47468,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -47521,7 +47521,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -47574,7 +47574,7 @@
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -47627,7 +47627,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -47680,7 +47680,7 @@
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -47733,7 +47733,7 @@
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -47786,7 +47786,7 @@
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -47839,7 +47839,7 @@
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -47892,7 +47892,7 @@
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -47945,7 +47945,7 @@
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -47998,7 +47998,7 @@
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -48051,7 +48051,7 @@
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -48104,7 +48104,7 @@
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -48157,7 +48157,7 @@
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -48210,7 +48210,7 @@
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -48263,7 +48263,7 @@
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
@@ -48316,7 +48316,7 @@
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -48369,7 +48369,7 @@
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -48422,7 +48422,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -48475,7 +48475,7 @@
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -48528,7 +48528,7 @@
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -48581,7 +48581,7 @@
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -48634,7 +48634,7 @@
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -48687,7 +48687,7 @@
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
@@ -48740,7 +48740,7 @@
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:35</t>
+          <t>2026-10-22 12:11:06</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>

--- a/data/SCRAPING_REKAP_DAMPAK_BENCANA_ENDE_LATEST.xlsx
+++ b/data/SCRAPING_REKAP_DAMPAK_BENCANA_ENDE_LATEST.xlsx
@@ -17041,7 +17041,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -17126,7 +17126,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -17209,7 +17209,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -17292,7 +17292,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -17375,7 +17375,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -17545,7 +17545,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -17628,7 +17628,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -17711,7 +17711,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -17794,7 +17794,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -17877,7 +17877,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -17960,7 +17960,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -18043,7 +18043,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -18126,7 +18126,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -18209,7 +18209,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -18292,7 +18292,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -18375,7 +18375,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -18458,7 +18458,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -18541,7 +18541,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -18624,7 +18624,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -18707,7 +18707,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -18790,7 +18790,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -18873,7 +18873,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -18956,7 +18956,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -19039,7 +19039,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -19122,7 +19122,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -19205,7 +19205,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -19288,7 +19288,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -19371,7 +19371,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -19454,7 +19454,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -19539,7 +19539,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -19622,7 +19622,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -19705,7 +19705,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -19788,7 +19788,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -19871,7 +19871,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -19954,7 +19954,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -20037,7 +20037,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -20120,7 +20120,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -20203,7 +20203,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -20286,7 +20286,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -20369,7 +20369,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -20452,7 +20452,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -20535,7 +20535,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -20618,7 +20618,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -20701,7 +20701,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -20784,7 +20784,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -20867,7 +20867,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -20950,7 +20950,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -21033,7 +21033,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -21116,7 +21116,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -21199,7 +21199,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -21282,7 +21282,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -21365,7 +21365,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -21448,7 +21448,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -21531,7 +21531,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -21614,7 +21614,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -21697,7 +21697,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -21780,7 +21780,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -21865,7 +21865,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -21948,7 +21948,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -22031,7 +22031,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -22114,7 +22114,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -22197,7 +22197,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -22280,7 +22280,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -22363,7 +22363,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -22446,7 +22446,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -22529,7 +22529,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -22612,7 +22612,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -22695,7 +22695,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -22778,7 +22778,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -22861,7 +22861,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -22944,7 +22944,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -23027,7 +23027,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -23110,7 +23110,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -23193,7 +23193,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -23276,7 +23276,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -23361,7 +23361,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -23446,7 +23446,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -23529,7 +23529,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -23614,7 +23614,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -23701,7 +23701,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -23784,7 +23784,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -23867,7 +23867,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -23950,7 +23950,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -24037,7 +24037,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -24120,7 +24120,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -24203,7 +24203,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24286,7 +24286,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -24369,7 +24369,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -24452,7 +24452,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -24535,7 +24535,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -24618,7 +24618,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -24701,7 +24701,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -24784,7 +24784,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -24867,7 +24867,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -24950,7 +24950,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -25037,7 +25037,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -25120,7 +25120,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -25203,7 +25203,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -25286,7 +25286,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -25369,7 +25369,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -25452,7 +25452,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -25535,7 +25535,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -25618,7 +25618,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -25701,7 +25701,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -25784,7 +25784,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -25867,7 +25867,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -25950,7 +25950,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -26033,7 +26033,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -26118,7 +26118,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -26201,7 +26201,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -26284,7 +26284,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -26367,7 +26367,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -26450,7 +26450,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -26533,7 +26533,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -26616,7 +26616,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -26699,7 +26699,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -26782,7 +26782,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -26865,7 +26865,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -26950,7 +26950,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -27033,7 +27033,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -27116,7 +27116,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -27199,7 +27199,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -27282,7 +27282,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -27365,7 +27365,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -27448,7 +27448,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -27535,7 +27535,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -27618,7 +27618,7 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -27701,7 +27701,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -27786,7 +27786,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -27869,7 +27869,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -27952,7 +27952,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -28035,7 +28035,7 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -28118,7 +28118,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -28201,7 +28201,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -28284,7 +28284,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -28367,7 +28367,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -28450,7 +28450,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -28533,7 +28533,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -28616,7 +28616,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -28699,7 +28699,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -28782,7 +28782,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -28865,7 +28865,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -28948,7 +28948,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -29033,7 +29033,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -29116,7 +29116,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -29199,7 +29199,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -29282,7 +29282,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -29365,7 +29365,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -29448,7 +29448,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -29533,7 +29533,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -29616,7 +29616,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -29699,7 +29699,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -29782,7 +29782,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -29865,7 +29865,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -29948,7 +29948,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -30031,7 +30031,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -30114,7 +30114,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -30197,7 +30197,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -30280,7 +30280,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -30365,7 +30365,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -30448,7 +30448,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -30531,7 +30531,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -30614,7 +30614,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -30697,7 +30697,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -30784,7 +30784,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -30867,7 +30867,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -30950,7 +30950,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -31033,7 +31033,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -31118,7 +31118,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -31201,7 +31201,7 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -31284,7 +31284,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -31367,7 +31367,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -31450,7 +31450,7 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -31533,7 +31533,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -31616,7 +31616,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -31699,7 +31699,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -31782,7 +31782,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -31865,7 +31865,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -31948,7 +31948,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -32031,7 +32031,7 @@
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -32116,7 +32116,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -32199,7 +32199,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -32282,7 +32282,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -32365,7 +32365,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -32448,7 +32448,7 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -32531,7 +32531,7 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -32614,7 +32614,7 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -32697,7 +32697,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -32780,7 +32780,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -32863,7 +32863,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -32946,7 +32946,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -33029,7 +33029,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -33112,7 +33112,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -33195,7 +33195,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -33278,7 +33278,7 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -33361,7 +33361,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -33446,7 +33446,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -33531,7 +33531,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -33614,7 +33614,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -33697,7 +33697,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -33780,7 +33780,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -33863,7 +33863,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:02</t>
+          <t>2026-10-22 12:12:48</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -34059,7 +34059,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -34112,7 +34112,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -34165,7 +34165,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -34218,7 +34218,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -34271,7 +34271,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -34324,7 +34324,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -34377,7 +34377,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -34430,7 +34430,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -34483,7 +34483,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -34536,7 +34536,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -34589,7 +34589,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -34642,7 +34642,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -34695,7 +34695,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -34748,7 +34748,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -34801,7 +34801,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -34854,7 +34854,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -34907,7 +34907,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -34960,7 +34960,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -35013,7 +35013,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -35066,7 +35066,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -35119,7 +35119,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -35172,7 +35172,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -35225,7 +35225,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -35278,7 +35278,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -35331,7 +35331,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -35384,7 +35384,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -35437,7 +35437,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -35490,7 +35490,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -35543,7 +35543,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -35596,7 +35596,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -35649,7 +35649,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -35755,7 +35755,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -35808,7 +35808,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -35861,7 +35861,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -35914,7 +35914,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -35967,7 +35967,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -36020,7 +36020,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -36073,7 +36073,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -36126,7 +36126,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -36179,7 +36179,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -36232,7 +36232,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -36285,7 +36285,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -36338,7 +36338,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -36391,7 +36391,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -36444,7 +36444,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -36497,7 +36497,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -36550,7 +36550,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -36603,7 +36603,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -36656,7 +36656,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -36709,7 +36709,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -36762,7 +36762,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -36815,7 +36815,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -36868,7 +36868,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -36921,7 +36921,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -36974,7 +36974,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -37027,7 +37027,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -37080,7 +37080,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -37133,7 +37133,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -37186,7 +37186,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -37239,7 +37239,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -37292,7 +37292,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -37345,7 +37345,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -37398,7 +37398,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -37451,7 +37451,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -37504,7 +37504,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -37557,7 +37557,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -37610,7 +37610,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -37663,7 +37663,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -37716,7 +37716,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -37769,7 +37769,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -37822,7 +37822,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -37875,7 +37875,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -37928,7 +37928,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -37981,7 +37981,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -38034,7 +38034,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -38087,7 +38087,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -38140,7 +38140,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -38193,7 +38193,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -38246,7 +38246,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -38299,7 +38299,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -38352,7 +38352,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -38405,7 +38405,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -38458,7 +38458,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -38511,7 +38511,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -38564,7 +38564,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -38617,7 +38617,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -38670,7 +38670,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -38723,7 +38723,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -38776,7 +38776,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -38829,7 +38829,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -38882,7 +38882,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -38935,7 +38935,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -38988,7 +38988,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -39041,7 +39041,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -39094,7 +39094,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -39147,7 +39147,7 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -39200,7 +39200,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -39253,7 +39253,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -39306,7 +39306,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -39359,7 +39359,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -39412,7 +39412,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -39465,7 +39465,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -39518,7 +39518,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -39571,7 +39571,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -39624,7 +39624,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -39677,7 +39677,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -39730,7 +39730,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -39783,7 +39783,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -39836,7 +39836,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -39889,7 +39889,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -39942,7 +39942,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -39995,7 +39995,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -40048,7 +40048,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -40101,7 +40101,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -40154,7 +40154,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -40207,7 +40207,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -40260,7 +40260,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -40313,7 +40313,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -40366,7 +40366,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -40419,7 +40419,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -40472,7 +40472,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -40525,7 +40525,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -40578,7 +40578,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -40631,7 +40631,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -40684,7 +40684,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -40737,7 +40737,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -40790,7 +40790,7 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -40843,7 +40843,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -40896,7 +40896,7 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -40949,7 +40949,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -41002,7 +41002,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -41055,7 +41055,7 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -41108,7 +41108,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -41161,7 +41161,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -41214,7 +41214,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -41320,7 +41320,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -41373,7 +41373,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -41426,7 +41426,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -41479,7 +41479,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -41532,7 +41532,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -41585,7 +41585,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -41638,7 +41638,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -41691,7 +41691,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -41744,7 +41744,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -41797,7 +41797,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -41850,7 +41850,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -41903,7 +41903,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -41956,7 +41956,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -42009,7 +42009,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -42062,7 +42062,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -42115,7 +42115,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -42168,7 +42168,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -42221,7 +42221,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -42274,7 +42274,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -42327,7 +42327,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -42380,7 +42380,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -42433,7 +42433,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -42486,7 +42486,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -42539,7 +42539,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -42592,7 +42592,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -42645,7 +42645,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -42698,7 +42698,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -42751,7 +42751,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -42804,7 +42804,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -42857,7 +42857,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -42910,7 +42910,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -42963,7 +42963,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -43016,7 +43016,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -43069,7 +43069,7 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -43122,7 +43122,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -43175,7 +43175,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -43228,7 +43228,7 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -43281,7 +43281,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -43334,7 +43334,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -43387,7 +43387,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -43440,7 +43440,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -43493,7 +43493,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -43546,7 +43546,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -43599,7 +43599,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -43652,7 +43652,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -43705,7 +43705,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -43758,7 +43758,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -43811,7 +43811,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -43864,7 +43864,7 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -43917,7 +43917,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -43970,7 +43970,7 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -44023,7 +44023,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -44076,7 +44076,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -44129,7 +44129,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -44182,7 +44182,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -44235,7 +44235,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -44288,7 +44288,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -44341,7 +44341,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -44394,7 +44394,7 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -44447,7 +44447,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -44500,7 +44500,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -44553,7 +44553,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -44606,7 +44606,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -44659,7 +44659,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -44712,7 +44712,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -44765,7 +44765,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -44818,7 +44818,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -44871,7 +44871,7 @@
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -44924,7 +44924,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -44977,7 +44977,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -45030,7 +45030,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -45083,7 +45083,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -45136,7 +45136,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -45189,7 +45189,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -45242,7 +45242,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -45295,7 +45295,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -45348,7 +45348,7 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -45401,7 +45401,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -45454,7 +45454,7 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -45507,7 +45507,7 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -45560,7 +45560,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -45613,7 +45613,7 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -45666,7 +45666,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -45719,7 +45719,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -45772,7 +45772,7 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -45825,7 +45825,7 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -45878,7 +45878,7 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -45931,7 +45931,7 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -45984,7 +45984,7 @@
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -46037,7 +46037,7 @@
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -46090,7 +46090,7 @@
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -46143,7 +46143,7 @@
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -46196,7 +46196,7 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -46249,7 +46249,7 @@
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -46302,7 +46302,7 @@
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -46355,7 +46355,7 @@
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -46408,7 +46408,7 @@
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -46461,7 +46461,7 @@
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -46514,7 +46514,7 @@
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -46567,7 +46567,7 @@
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -46620,7 +46620,7 @@
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -46673,7 +46673,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -46726,7 +46726,7 @@
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -46779,7 +46779,7 @@
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -46832,7 +46832,7 @@
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -46885,7 +46885,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -46938,7 +46938,7 @@
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -46991,7 +46991,7 @@
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -47044,7 +47044,7 @@
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -47097,7 +47097,7 @@
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -47150,7 +47150,7 @@
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -47203,7 +47203,7 @@
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -47256,7 +47256,7 @@
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -47309,7 +47309,7 @@
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -47362,7 +47362,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -47415,7 +47415,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -47468,7 +47468,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -47521,7 +47521,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -47574,7 +47574,7 @@
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -47627,7 +47627,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -47680,7 +47680,7 @@
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -47733,7 +47733,7 @@
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -47786,7 +47786,7 @@
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -47839,7 +47839,7 @@
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -47892,7 +47892,7 @@
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -47945,7 +47945,7 @@
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -47998,7 +47998,7 @@
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -48051,7 +48051,7 @@
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -48104,7 +48104,7 @@
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -48157,7 +48157,7 @@
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -48210,7 +48210,7 @@
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -48263,7 +48263,7 @@
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
@@ -48316,7 +48316,7 @@
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -48369,7 +48369,7 @@
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -48422,7 +48422,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -48475,7 +48475,7 @@
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -48528,7 +48528,7 @@
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -48581,7 +48581,7 @@
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -48634,7 +48634,7 @@
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -48687,7 +48687,7 @@
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
@@ -48740,7 +48740,7 @@
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
-          <t>2026-10-22 12:11:06</t>
+          <t>2026-10-22 12:12:52</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>

--- a/data/SCRAPING_REKAP_DAMPAK_BENCANA_ENDE_LATEST.xlsx
+++ b/data/SCRAPING_REKAP_DAMPAK_BENCANA_ENDE_LATEST.xlsx
@@ -574,7 +574,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -659,7 +659,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -744,7 +744,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -829,7 +829,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -918,7 +918,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1088,7 +1088,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1173,7 +1173,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1258,7 +1258,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1345,7 +1345,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1430,7 +1430,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1515,7 +1515,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1600,7 +1600,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1685,7 +1685,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1770,7 +1770,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1855,7 +1855,7 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1940,7 +1940,7 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2025,7 +2025,7 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2110,7 +2110,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2195,7 +2195,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2280,7 +2280,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2365,7 +2365,7 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2452,7 +2452,7 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2537,7 +2537,7 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2622,7 +2622,7 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2707,7 +2707,7 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2792,7 +2792,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2877,7 +2877,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2962,7 +2962,7 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3047,7 +3047,7 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3132,7 +3132,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3217,7 +3217,7 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3302,7 +3302,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3387,7 +3387,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3472,7 +3472,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3557,7 +3557,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3642,7 +3642,7 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3727,7 +3727,7 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3812,7 +3812,7 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3897,7 +3897,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3982,7 +3982,7 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4067,7 +4067,7 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4152,7 +4152,7 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4237,7 +4237,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4322,7 +4322,7 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4407,7 +4407,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4492,7 +4492,7 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4577,7 +4577,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4662,7 +4662,7 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4747,7 +4747,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4832,7 +4832,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4917,7 +4917,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5002,7 +5002,7 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5089,7 +5089,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5178,7 +5178,7 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5263,7 +5263,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5348,7 +5348,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5433,7 +5433,7 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5518,7 +5518,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5603,7 +5603,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5688,7 +5688,7 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5773,7 +5773,7 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5860,7 +5860,7 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5945,7 +5945,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6030,7 +6030,7 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6115,7 +6115,7 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6200,7 +6200,7 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6285,7 +6285,7 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6370,7 +6370,7 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6455,7 +6455,7 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6540,7 +6540,7 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6625,7 +6625,7 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6710,7 +6710,7 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6795,7 +6795,7 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6880,7 +6880,7 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6965,7 +6965,7 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7050,7 +7050,7 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7135,7 +7135,7 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7220,7 +7220,7 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7305,7 +7305,7 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7390,7 +7390,7 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7475,7 +7475,7 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7560,7 +7560,7 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7645,7 +7645,7 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7730,7 +7730,7 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7815,7 +7815,7 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7900,7 +7900,7 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7985,7 +7985,7 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8072,7 +8072,7 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8157,7 +8157,7 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8242,7 +8242,7 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8327,7 +8327,7 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -8412,7 +8412,7 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -8497,7 +8497,7 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8582,7 +8582,7 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -8667,7 +8667,7 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -8752,7 +8752,7 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8837,7 +8837,7 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8922,7 +8922,7 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9007,7 +9007,7 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9094,7 +9094,7 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -9179,7 +9179,7 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9264,7 +9264,7 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -9349,7 +9349,7 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -9434,7 +9434,7 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -9519,7 +9519,7 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -9606,7 +9606,7 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -9691,7 +9691,7 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -9776,7 +9776,7 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -9861,7 +9861,7 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -9946,7 +9946,7 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -10031,7 +10031,7 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -10116,7 +10116,7 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -10201,7 +10201,7 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -10286,7 +10286,7 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -10371,7 +10371,7 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -10456,7 +10456,7 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -10541,7 +10541,7 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -10628,7 +10628,7 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -10713,7 +10713,7 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -10800,7 +10800,7 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -10885,7 +10885,7 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -10970,7 +10970,7 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -11055,7 +11055,7 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -11140,7 +11140,7 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -11225,7 +11225,7 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -11310,7 +11310,7 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -11395,7 +11395,7 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -11480,7 +11480,7 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -11565,7 +11565,7 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -11650,7 +11650,7 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -11735,7 +11735,7 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -11820,7 +11820,7 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -11905,7 +11905,7 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -11990,7 +11990,7 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -12075,7 +12075,7 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -12160,7 +12160,7 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -12245,7 +12245,7 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -12330,7 +12330,7 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -12415,7 +12415,7 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -12500,7 +12500,7 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -12587,7 +12587,7 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -12674,7 +12674,7 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -12759,7 +12759,7 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -12844,7 +12844,7 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -12929,7 +12929,7 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -13107,7 +13107,7 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -13192,7 +13192,7 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -13277,7 +13277,7 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -13453,7 +13453,7 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -13538,7 +13538,7 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -13623,7 +13623,7 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -13710,7 +13710,7 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -13797,7 +13797,7 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -13882,7 +13882,7 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -13967,7 +13967,7 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -14052,7 +14052,7 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -14137,7 +14137,7 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -14224,7 +14224,7 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -14309,7 +14309,7 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -14394,7 +14394,7 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -14479,7 +14479,7 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -14564,7 +14564,7 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -14649,7 +14649,7 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -14734,7 +14734,7 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -14821,7 +14821,7 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -14906,7 +14906,7 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -14991,7 +14991,7 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -15076,7 +15076,7 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -15161,7 +15161,7 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -15246,7 +15246,7 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -15331,7 +15331,7 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -15416,7 +15416,7 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -15503,7 +15503,7 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -15588,7 +15588,7 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -15673,7 +15673,7 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -15758,7 +15758,7 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -15845,7 +15845,7 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -15930,7 +15930,7 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -16017,7 +16017,7 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -16102,7 +16102,7 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -16187,7 +16187,7 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -16272,7 +16272,7 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -16357,7 +16357,7 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -16442,7 +16442,7 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -16527,7 +16527,7 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -16614,7 +16614,7 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -16703,7 +16703,7 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -16788,7 +16788,7 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -16877,7 +16877,7 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -16962,7 +16962,7 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -17047,7 +17047,7 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -17132,7 +17132,7 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -17217,7 +17217,7 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -17302,7 +17302,7 @@
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -17387,7 +17387,7 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -17472,7 +17472,7 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -17557,7 +17557,7 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -17642,7 +17642,7 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -17727,7 +17727,7 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:55</t>
+          <t>2026-10-22 13:45:46</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -17923,7 +17923,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -17976,7 +17976,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -18029,7 +18029,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -18082,7 +18082,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -18135,7 +18135,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -18188,7 +18188,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -18241,7 +18241,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -18294,7 +18294,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -18347,7 +18347,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -18400,7 +18400,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -18453,7 +18453,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -18506,7 +18506,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -18559,7 +18559,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -18612,7 +18612,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -18665,7 +18665,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -18718,7 +18718,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -18771,7 +18771,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -18824,7 +18824,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -18877,7 +18877,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -18930,7 +18930,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -18983,7 +18983,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -19036,7 +19036,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -19089,7 +19089,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -19195,7 +19195,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -19248,7 +19248,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -19301,7 +19301,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -19354,7 +19354,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -19407,7 +19407,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -19460,7 +19460,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -19513,7 +19513,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -19566,7 +19566,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -19619,7 +19619,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -19672,7 +19672,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -19725,7 +19725,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -19778,7 +19778,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -19831,7 +19831,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -19884,7 +19884,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -19937,7 +19937,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -19990,7 +19990,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -20043,7 +20043,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -20096,7 +20096,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -20149,7 +20149,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -20202,7 +20202,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -20255,7 +20255,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -20308,7 +20308,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -20361,7 +20361,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -20414,7 +20414,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -20467,7 +20467,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -20520,7 +20520,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -20573,7 +20573,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -20626,7 +20626,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -20679,7 +20679,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -20732,7 +20732,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -20785,7 +20785,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -20838,7 +20838,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -20891,7 +20891,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -20944,7 +20944,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -20997,7 +20997,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -21050,7 +21050,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -21103,7 +21103,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -21156,7 +21156,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -21209,7 +21209,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -21262,7 +21262,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -21368,7 +21368,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -21421,7 +21421,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -21474,7 +21474,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -21527,7 +21527,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -21580,7 +21580,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -21633,7 +21633,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -21739,7 +21739,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -21792,7 +21792,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -21845,7 +21845,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -21898,7 +21898,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -21951,7 +21951,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -22004,7 +22004,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -22057,7 +22057,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -22110,7 +22110,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -22163,7 +22163,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -22216,7 +22216,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -22269,7 +22269,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -22322,7 +22322,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -22375,7 +22375,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -22428,7 +22428,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -22534,7 +22534,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -22587,7 +22587,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -22640,7 +22640,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -22693,7 +22693,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -22746,7 +22746,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -22799,7 +22799,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -22852,7 +22852,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -22905,7 +22905,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -22958,7 +22958,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -23011,7 +23011,7 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -23064,7 +23064,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -23117,7 +23117,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -23170,7 +23170,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -23223,7 +23223,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -23276,7 +23276,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -23329,7 +23329,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -23382,7 +23382,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -23435,7 +23435,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -23488,7 +23488,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -23541,7 +23541,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -23594,7 +23594,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -23647,7 +23647,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -23700,7 +23700,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -23753,7 +23753,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -23806,7 +23806,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -23859,7 +23859,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -23912,7 +23912,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -23965,7 +23965,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -24018,7 +24018,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -24071,7 +24071,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -24124,7 +24124,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -24177,7 +24177,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -24283,7 +24283,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -24336,7 +24336,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -24389,7 +24389,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -24442,7 +24442,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -24495,7 +24495,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -24548,7 +24548,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -24601,7 +24601,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -24654,7 +24654,7 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -24707,7 +24707,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -24760,7 +24760,7 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -24813,7 +24813,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -24866,7 +24866,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -24919,7 +24919,7 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -24972,7 +24972,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -25025,7 +25025,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -25078,7 +25078,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -25131,7 +25131,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -25184,7 +25184,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -25237,7 +25237,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -25290,7 +25290,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -25343,7 +25343,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -25396,7 +25396,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -25449,7 +25449,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -25502,7 +25502,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -25555,7 +25555,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -25608,7 +25608,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -25661,7 +25661,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -25714,7 +25714,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -25767,7 +25767,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -25820,7 +25820,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -25873,7 +25873,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -25926,7 +25926,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -25979,7 +25979,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -26032,7 +26032,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -26085,7 +26085,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -26138,7 +26138,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -26191,7 +26191,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -26244,7 +26244,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -26297,7 +26297,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -26350,7 +26350,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -26403,7 +26403,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -26456,7 +26456,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -26509,7 +26509,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -26562,7 +26562,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -26615,7 +26615,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -26668,7 +26668,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -26721,7 +26721,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -26827,7 +26827,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -26880,7 +26880,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -26933,7 +26933,7 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -26986,7 +26986,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -27039,7 +27039,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -27092,7 +27092,7 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -27145,7 +27145,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -27198,7 +27198,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -27251,7 +27251,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -27304,7 +27304,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -27357,7 +27357,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -27410,7 +27410,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -27463,7 +27463,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -27516,7 +27516,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -27569,7 +27569,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -27622,7 +27622,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -27675,7 +27675,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -27728,7 +27728,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -27781,7 +27781,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -27834,7 +27834,7 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -27887,7 +27887,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -27940,7 +27940,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -27993,7 +27993,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -28046,7 +28046,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -28099,7 +28099,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -28152,7 +28152,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -28205,7 +28205,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -28258,7 +28258,7 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -28311,7 +28311,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -28364,7 +28364,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -28417,7 +28417,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -28470,7 +28470,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -28523,7 +28523,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -28576,7 +28576,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -28629,7 +28629,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -28682,7 +28682,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -28735,7 +28735,7 @@
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -28788,7 +28788,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -28841,7 +28841,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -28894,7 +28894,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -28947,7 +28947,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -29000,7 +29000,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -29053,7 +29053,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -29106,7 +29106,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -29159,7 +29159,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -29212,7 +29212,7 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -29265,7 +29265,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -29371,7 +29371,7 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -29424,7 +29424,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -29477,7 +29477,7 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -29530,7 +29530,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -29583,7 +29583,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -29636,7 +29636,7 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -29689,7 +29689,7 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -29742,7 +29742,7 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -29795,7 +29795,7 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -29848,7 +29848,7 @@
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -29901,7 +29901,7 @@
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -29954,7 +29954,7 @@
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -30007,7 +30007,7 @@
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -30060,7 +30060,7 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -30113,7 +30113,7 @@
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -30166,7 +30166,7 @@
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -30219,7 +30219,7 @@
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -30272,7 +30272,7 @@
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -30325,7 +30325,7 @@
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -30378,7 +30378,7 @@
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -30431,7 +30431,7 @@
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -30484,7 +30484,7 @@
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -30590,7 +30590,7 @@
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -30643,7 +30643,7 @@
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -30696,7 +30696,7 @@
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -30802,7 +30802,7 @@
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -30855,7 +30855,7 @@
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -30908,7 +30908,7 @@
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -30961,7 +30961,7 @@
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -31014,7 +31014,7 @@
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -31067,7 +31067,7 @@
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -31120,7 +31120,7 @@
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -31173,7 +31173,7 @@
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -31226,7 +31226,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -31279,7 +31279,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -31332,7 +31332,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -31385,7 +31385,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -31438,7 +31438,7 @@
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -31491,7 +31491,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -31544,7 +31544,7 @@
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -31597,7 +31597,7 @@
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -31650,7 +31650,7 @@
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -31703,7 +31703,7 @@
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -31756,7 +31756,7 @@
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -31809,7 +31809,7 @@
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -31915,7 +31915,7 @@
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -31968,7 +31968,7 @@
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -32021,7 +32021,7 @@
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -32074,7 +32074,7 @@
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -32127,7 +32127,7 @@
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
@@ -32180,7 +32180,7 @@
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -32233,7 +32233,7 @@
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -32286,7 +32286,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -32339,7 +32339,7 @@
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -32392,7 +32392,7 @@
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -32445,7 +32445,7 @@
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -32498,7 +32498,7 @@
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -32551,7 +32551,7 @@
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
@@ -32604,7 +32604,7 @@
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
-          <t>2026-10-22 13:41:58</t>
+          <t>2026-10-22 13:45:49</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
